--- a/daq_system/inputs/CMS_Master_Control_Wiring_Dev6.xlsx
+++ b/daq_system/inputs/CMS_Master_Control_Wiring_Dev6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\School\Documents\repos\DAQ\daq_system\inputs\CMS\pneumatic-press\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmaso\Documents\DAQ\PSPL_DAQ\daq_system\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73921C6B-1B33-47F2-9F85-71BF36A5F983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271AA39E-62F7-4AF8-BCDB-B7EC328D0FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67" yWindow="413" windowWidth="12733" windowHeight="7720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DO" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -63,6 +63,24 @@
   </si>
   <si>
     <t>Wiring DO</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>CAMERA</t>
+  </si>
+  <si>
+    <t>HS_CAMERA</t>
+  </si>
+  <si>
+    <t>dev6/port0/line27</t>
+  </si>
+  <si>
+    <t>dev6/port0/line30</t>
   </si>
 </sst>
 </file>
@@ -72,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +239,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1002,19 +1026,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U13"/>
-  <sheetFormatPr defaultColWidth="9.1171875" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:U14"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.41015625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.703125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.29296875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.1171875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="36.87890625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="10.5859375" style="7" customWidth="1"/>
-    <col min="7" max="16384" width="9.1171875" style="4"/>
+    <col min="1" max="1" width="19.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="31.73046875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.1328125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="36.86328125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.1328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1051,57 +1075,83 @@
       <c r="T1" s="11"/>
       <c r="U1" s="11"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="B2"/>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.5">
-      <c r="B3"/>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B4"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B5"/>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B6"/>
       <c r="E6" s="10"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B7"/>
       <c r="E7" s="10"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B8"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B9"/>
       <c r="E9" s="10"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B10"/>
       <c r="E10" s="10"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B11"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B12"/>
       <c r="E12" s="10"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
       <c r="B13"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="B14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:U1"/>
   </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C11" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"NC,NO,norm_off,norm_on"</formula1>
@@ -1118,22 +1168,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T21"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="30.41015625" customWidth="1"/>
-    <col min="3" max="3" width="21.87890625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.41015625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5859375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.87890625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5859375" customWidth="1"/>
-    <col min="10" max="10" width="32.1171875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1171875" style="3"/>
+    <col min="2" max="2" width="30.3984375" customWidth="1"/>
+    <col min="3" max="3" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.59765625" customWidth="1"/>
+    <col min="10" max="10" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1177,7 +1227,7 @@
       <c r="S1" s="13"/>
       <c r="T1" s="13"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="4"/>
@@ -1188,7 +1238,7 @@
       <c r="I2" s="4"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1196,7 +1246,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1204,7 +1254,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1212,7 +1262,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1220,7 +1270,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1228,7 +1278,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1236,7 +1286,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1246,7 +1296,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1256,7 +1306,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1266,7 +1316,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -1276,7 +1326,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1286,28 +1336,28 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B21" s="1"/>
     </row>
   </sheetData>
